--- a/artfynd/A 39991-2024 artfynd.xlsx
+++ b/artfynd/A 39991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119796499</v>
+        <v>119796508</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759812</v>
+        <v>759466</v>
       </c>
       <c r="R2" t="n">
-        <v>7325050</v>
+        <v>7325140</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796500</v>
+        <v>119796499</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759815</v>
+        <v>759812</v>
       </c>
       <c r="R3" t="n">
-        <v>7325060</v>
+        <v>7325050</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796508</v>
+        <v>119796506</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759466</v>
+        <v>759611</v>
       </c>
       <c r="R5" t="n">
-        <v>7325140</v>
+        <v>7325200</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796504</v>
+        <v>119796507</v>
       </c>
       <c r="B6" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759649</v>
+        <v>759586</v>
       </c>
       <c r="R6" t="n">
-        <v>7325130</v>
+        <v>7325210</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796502</v>
+        <v>119796504</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759744</v>
+        <v>759649</v>
       </c>
       <c r="R7" t="n">
-        <v>7325080</v>
+        <v>7325130</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796507</v>
+        <v>119796502</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759586</v>
+        <v>759744</v>
       </c>
       <c r="R8" t="n">
-        <v>7325210</v>
+        <v>7325080</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796509</v>
+        <v>119796500</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759480</v>
+        <v>759815</v>
       </c>
       <c r="R9" t="n">
-        <v>7325130</v>
+        <v>7325060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796506</v>
+        <v>119796509</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759611</v>
+        <v>759480</v>
       </c>
       <c r="R10" t="n">
-        <v>7325200</v>
+        <v>7325130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 39991-2024 artfynd.xlsx
+++ b/artfynd/A 39991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119796508</v>
+        <v>119796502</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759466</v>
+        <v>759744</v>
       </c>
       <c r="R2" t="n">
-        <v>7325140</v>
+        <v>7325080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796499</v>
+        <v>119796500</v>
       </c>
       <c r="B3" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759812</v>
+        <v>759815</v>
       </c>
       <c r="R3" t="n">
-        <v>7325050</v>
+        <v>7325060</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796503</v>
+        <v>119796507</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759723</v>
+        <v>759586</v>
       </c>
       <c r="R4" t="n">
-        <v>7325060</v>
+        <v>7325210</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796506</v>
+        <v>119796503</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759611</v>
+        <v>759723</v>
       </c>
       <c r="R5" t="n">
-        <v>7325200</v>
+        <v>7325060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796507</v>
+        <v>119796508</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759586</v>
+        <v>759466</v>
       </c>
       <c r="R6" t="n">
-        <v>7325210</v>
+        <v>7325140</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796504</v>
+        <v>119796506</v>
       </c>
       <c r="B7" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759649</v>
+        <v>759611</v>
       </c>
       <c r="R7" t="n">
-        <v>7325130</v>
+        <v>7325200</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796502</v>
+        <v>119796509</v>
       </c>
       <c r="B8" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759744</v>
+        <v>759480</v>
       </c>
       <c r="R8" t="n">
-        <v>7325080</v>
+        <v>7325130</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796500</v>
+        <v>119796504</v>
       </c>
       <c r="B9" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759815</v>
+        <v>759649</v>
       </c>
       <c r="R9" t="n">
-        <v>7325060</v>
+        <v>7325130</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796509</v>
+        <v>119796499</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759480</v>
+        <v>759812</v>
       </c>
       <c r="R10" t="n">
-        <v>7325130</v>
+        <v>7325050</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 39991-2024 artfynd.xlsx
+++ b/artfynd/A 39991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119796502</v>
+        <v>119796504</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759744</v>
+        <v>759649</v>
       </c>
       <c r="R2" t="n">
-        <v>7325080</v>
+        <v>7325130</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796500</v>
+        <v>119796506</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759815</v>
+        <v>759611</v>
       </c>
       <c r="R3" t="n">
-        <v>7325060</v>
+        <v>7325200</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796507</v>
+        <v>119796508</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759586</v>
+        <v>759466</v>
       </c>
       <c r="R4" t="n">
-        <v>7325210</v>
+        <v>7325140</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796503</v>
+        <v>119796499</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759723</v>
+        <v>759812</v>
       </c>
       <c r="R5" t="n">
-        <v>7325060</v>
+        <v>7325050</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796508</v>
+        <v>119796502</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759466</v>
+        <v>759744</v>
       </c>
       <c r="R6" t="n">
-        <v>7325140</v>
+        <v>7325080</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796506</v>
+        <v>119796500</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759611</v>
+        <v>759815</v>
       </c>
       <c r="R7" t="n">
-        <v>7325200</v>
+        <v>7325060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796509</v>
+        <v>119796507</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759480</v>
+        <v>759586</v>
       </c>
       <c r="R8" t="n">
-        <v>7325130</v>
+        <v>7325210</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796504</v>
+        <v>119796503</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759649</v>
+        <v>759723</v>
       </c>
       <c r="R9" t="n">
-        <v>7325130</v>
+        <v>7325060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796499</v>
+        <v>119796509</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759812</v>
+        <v>759480</v>
       </c>
       <c r="R10" t="n">
-        <v>7325050</v>
+        <v>7325130</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 39991-2024 artfynd.xlsx
+++ b/artfynd/A 39991-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119796504</v>
       </c>
       <c r="B2" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796506</v>
+        <v>119796500</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91858</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759611</v>
+        <v>759815</v>
       </c>
       <c r="R3" t="n">
-        <v>7325200</v>
+        <v>7325060</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796508</v>
+        <v>119796506</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759466</v>
+        <v>759611</v>
       </c>
       <c r="R4" t="n">
-        <v>7325140</v>
+        <v>7325200</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796499</v>
+        <v>119796507</v>
       </c>
       <c r="B5" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759812</v>
+        <v>759586</v>
       </c>
       <c r="R5" t="n">
-        <v>7325050</v>
+        <v>7325210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796502</v>
+        <v>119796508</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759744</v>
+        <v>759466</v>
       </c>
       <c r="R6" t="n">
-        <v>7325080</v>
+        <v>7325140</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796500</v>
+        <v>119796502</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759815</v>
+        <v>759744</v>
       </c>
       <c r="R7" t="n">
-        <v>7325060</v>
+        <v>7325080</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796507</v>
+        <v>119796499</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759586</v>
+        <v>759812</v>
       </c>
       <c r="R8" t="n">
-        <v>7325210</v>
+        <v>7325050</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1455,7 @@
         <v>119796503</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>119796509</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>91870</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 39991-2024 artfynd.xlsx
+++ b/artfynd/A 39991-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119796504</v>
+        <v>119796507</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759649</v>
+        <v>759586</v>
       </c>
       <c r="R2" t="n">
-        <v>7325130</v>
+        <v>7325210</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796500</v>
+        <v>119796504</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759815</v>
+        <v>759649</v>
       </c>
       <c r="R3" t="n">
-        <v>7325060</v>
+        <v>7325130</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796506</v>
+        <v>119796508</v>
       </c>
       <c r="B4" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759611</v>
+        <v>759466</v>
       </c>
       <c r="R4" t="n">
-        <v>7325200</v>
+        <v>7325140</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119796507</v>
+        <v>119796503</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>91870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759586</v>
+        <v>759723</v>
       </c>
       <c r="R5" t="n">
-        <v>7325210</v>
+        <v>7325060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119796508</v>
+        <v>119796509</v>
       </c>
       <c r="B6" t="n">
-        <v>91902</v>
+        <v>91870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759466</v>
+        <v>759480</v>
       </c>
       <c r="R6" t="n">
-        <v>7325140</v>
+        <v>7325130</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119796502</v>
+        <v>119796506</v>
       </c>
       <c r="B7" t="n">
         <v>91850</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759744</v>
+        <v>759611</v>
       </c>
       <c r="R7" t="n">
-        <v>7325080</v>
+        <v>7325200</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119796499</v>
+        <v>119796500</v>
       </c>
       <c r="B8" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>759812</v>
+        <v>759815</v>
       </c>
       <c r="R8" t="n">
-        <v>7325050</v>
+        <v>7325060</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119796503</v>
+        <v>119796502</v>
       </c>
       <c r="B9" t="n">
-        <v>91870</v>
+        <v>91850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>759723</v>
+        <v>759744</v>
       </c>
       <c r="R9" t="n">
-        <v>7325060</v>
+        <v>7325080</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119796509</v>
+        <v>119796499</v>
       </c>
       <c r="B10" t="n">
-        <v>91870</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1607,10 +1607,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>759480</v>
+        <v>759812</v>
       </c>
       <c r="R10" t="n">
-        <v>7325130</v>
+        <v>7325050</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 39991-2024 artfynd.xlsx
+++ b/artfynd/A 39991-2024 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119796504</v>
+        <v>119796508</v>
       </c>
       <c r="B3" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759649</v>
+        <v>759466</v>
       </c>
       <c r="R3" t="n">
-        <v>7325130</v>
+        <v>7325140</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119796508</v>
+        <v>119796504</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759466</v>
+        <v>759649</v>
       </c>
       <c r="R4" t="n">
-        <v>7325140</v>
+        <v>7325130</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
